--- a/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1954295-D6F7-1144-AAFC-1E0B51918B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E0CBB3-E13B-3541-9A7D-8D44CFF84267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="tbl_samples" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data_dictionary!$A$4:$D$74</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="294">
   <si>
     <t>Field Name</t>
   </si>
@@ -1212,6 +1212,12 @@
   <si>
     <t>Whether the sample is an Individual, Composite, Mean, SD, or Equation</t>
   </si>
+  <si>
+    <t xml:space="preserve">The type of lipid correction done for isotope values </t>
+  </si>
+  <si>
+    <t>as in: bulk; format: character</t>
+  </si>
 </sst>
 </file>
 
@@ -1905,7 +1911,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDB0B4B-8041-E244-B061-95D35DE0CD3B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
@@ -2832,13 +2838,13 @@
         <v>39</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>36</v>
+        <v>215</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>62</v>
+        <v>293</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>57</v>
+        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -2846,13 +2852,13 @@
         <v>39</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -2860,13 +2866,13 @@
         <v>39</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C70" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D70" s="30" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -2874,13 +2880,13 @@
         <v>39</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>218</v>
+        <v>38</v>
       </c>
       <c r="C71" s="30" t="s">
-        <v>222</v>
+        <v>64</v>
       </c>
       <c r="D71" s="30" t="s">
-        <v>219</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -2888,13 +2894,13 @@
         <v>39</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -2902,195 +2908,195 @@
         <v>39</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>144</v>
+        <v>221</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>145</v>
+        <v>223</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>146</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="B74" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="D74" s="30" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="B74" s="30" t="s">
+      <c r="B75" s="30" t="s">
         <v>225</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="C75" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="D74" s="30" t="s">
+      <c r="D75" s="30" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A75" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="B75" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="C75" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="D75" s="33" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A76" s="33" t="s">
         <v>224</v>
       </c>
       <c r="B76" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B77" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="C76" s="33" t="s">
+      <c r="C77" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D77" s="33" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A77" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="B77" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="C77" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D77" s="33" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="33" t="s">
         <v>234</v>
       </c>
       <c r="B78" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="D78" s="33" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+      <c r="A79" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="C79" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D79" s="33" t="s">
         <v>240</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="30" t="s">
-        <v>234</v>
-      </c>
-      <c r="B79" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="C79" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="D79" s="30" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="B80" s="30" t="s">
-        <v>245</v>
+        <v>234</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>287</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+      <c r="D80" s="30" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="30" t="s">
         <v>244</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>239</v>
+        <v>287</v>
       </c>
       <c r="D81" s="33" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
         <v>244</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>279</v>
-      </c>
-      <c r="D83" s="30" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="42" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="B84" s="40" t="s">
-        <v>276</v>
+      <c r="B84" s="30" t="s">
+        <v>251</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="D84" s="30" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
         <v>266</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D85" s="30" t="s">
-        <v>282</v>
+        <v>280</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
-        <v>264</v>
-      </c>
-      <c r="B86" s="30" t="s">
-        <v>253</v>
+        <v>266</v>
+      </c>
+      <c r="B86" s="40" t="s">
+        <v>277</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>254</v>
+        <v>282</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -3098,13 +3104,13 @@
         <v>264</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -3112,13 +3118,13 @@
         <v>264</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -3126,13 +3132,13 @@
         <v>264</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -3140,12 +3146,26 @@
         <v>264</v>
       </c>
       <c r="B90" s="30" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="D90" s="30" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="30" t="s">
+        <v>264</v>
+      </c>
+      <c r="B91" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C90" s="30" t="s">
+      <c r="C91" s="30" t="s">
         <v>262</v>
       </c>
-      <c r="D90" s="30" t="s">
+      <c r="D91" s="30" t="s">
         <v>263</v>
       </c>
     </row>

--- a/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E0CBB3-E13B-3541-9A7D-8D44CFF84267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4543AFA5-3716-3743-83CE-4904089D744D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -1213,10 +1213,10 @@
     <t>Whether the sample is an Individual, Composite, Mean, SD, or Equation</t>
   </si>
   <si>
-    <t xml:space="preserve">The type of lipid correction done for isotope values </t>
+    <t>as in: bulk; format: character</t>
   </si>
   <si>
-    <t>as in: bulk; format: character</t>
+    <t>The type of lipid correction applied to sample (i.e., bulk or lipid free)</t>
   </si>
 </sst>
 </file>
@@ -2833,7 +2833,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A68" s="30" t="s">
         <v>39</v>
       </c>
@@ -2841,10 +2841,10 @@
         <v>215</v>
       </c>
       <c r="C68" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D68" s="33" t="s">
         <v>293</v>
-      </c>
-      <c r="D68" s="30" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -44597,9 +44597,6 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R991" xr:uid="{C1262AB6-4400-D04A-976B-8F918C2989AD}">
       <formula1>"Total, Fork, Standard, Carapace"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L991" xr:uid="{8B693881-68ED-E14E-BF9E-57D22ABE1721}">
-      <formula1>"male, female, unknown, mixed"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F991" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
       <formula1>"spring, summer, fall, winter"</formula1>
     </dataValidation>
@@ -44651,6 +44648,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M10000" xr:uid="{03B901FA-1F79-BB4E-B6EE-6416D33DFA23}">
       <formula1>"fry, larva, nymph, pupa, juvenile, adult "</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L10000" xr:uid="{9EAB778A-B8BD-7744-BE56-7767011FBC78}">
+      <formula1>"male, female, unknown, both"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4543AFA5-3716-3743-83CE-4904089D744D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4A7243-FBD9-6F40-BD1B-B67056456E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -523,9 +523,6 @@
     <t>doi</t>
   </si>
   <si>
-    <t>tbl_source</t>
-  </si>
-  <si>
     <t>as in: Timothy B. Johnson; format: character</t>
   </si>
   <si>
@@ -745,9 +742,6 @@
     <t>Journal volume number</t>
   </si>
   <si>
-    <t>tbl_source;tbl_samples</t>
-  </si>
-  <si>
     <t>as in: Journal Article; format: character</t>
   </si>
   <si>
@@ -914,9 +908,6 @@
   </si>
   <si>
     <t>as in: Benjamin L. Hlina; format: character</t>
-  </si>
-  <si>
-    <t>This data dictionary is to guide you in filling out/interpreting the fields in tbl_submission, tbl_source,  and tbl_samples data sheet. This sheet does not need to be submitted with your data. Green fields are required when submitting the data</t>
   </si>
   <si>
     <t>as in: juvenile - (i.e., fry, larva, juvenile, and adult); format: character</t>
@@ -1217,6 +1208,15 @@
   </si>
   <si>
     <t>The type of lipid correction applied to sample (i.e., bulk or lipid free)</t>
+  </si>
+  <si>
+    <t>tbl_sources</t>
+  </si>
+  <si>
+    <t>tbl_sources;tbl_samples</t>
+  </si>
+  <si>
+    <t>This data dictionary is to guide you in filling out/interpreting the fields in tbl_submission, tbl_sources,  and tbl_samples data sheet. This sheet does not need to be submitted with your data. Green fields are required when submitting the data</t>
   </si>
 </sst>
 </file>
@@ -1923,7 +1923,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="48" t="s">
-        <v>207</v>
+        <v>293</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
@@ -1953,49 +1953,49 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>203</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="56" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>150</v>
+        <v>292</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>4</v>
@@ -2004,214 +2004,214 @@
         <v>66</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B9" s="27" t="s">
         <v>78</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B10" s="27" t="s">
         <v>79</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="56" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>80</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B12" s="27" t="s">
         <v>81</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>82</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="24" t="s">
         <v>94</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B18" s="24" t="s">
         <v>84</v>
       </c>
       <c r="C18" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D18" s="24" t="s">
         <v>97</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B19" s="24" t="s">
         <v>85</v>
       </c>
       <c r="C19" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" s="24" t="s">
         <v>99</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B20" s="24" t="s">
         <v>86</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="24" t="s">
         <v>101</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>103</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>88</v>
+        <v>291</v>
       </c>
       <c r="B22" s="24" t="s">
         <v>87</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>18</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="30" t="s">
         <v>40</v>
@@ -2233,69 +2233,69 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B27" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="D27" s="30" t="s">
         <v>108</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="30" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" s="32" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
@@ -2303,55 +2303,55 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D33" s="30" t="s">
         <v>41</v>
@@ -2359,21 +2359,21 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>13</v>
@@ -2382,29 +2382,29 @@
         <v>50</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>49</v>
@@ -2415,66 +2415,66 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>51</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B41" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="C41" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="D41" s="33" t="s">
         <v>288</v>
-      </c>
-      <c r="C41" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C42" s="30" t="s">
         <v>72</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B43" s="32" t="s">
         <v>9</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B44" s="32" t="s">
         <v>75</v>
@@ -2508,7 +2508,7 @@
         <v>76</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -2516,13 +2516,13 @@
         <v>16</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C45" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="30" t="s">
         <v>121</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -2547,10 +2547,10 @@
         <v>19</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -2564,7 +2564,7 @@
         <v>60</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -2575,7 +2575,7 @@
         <v>21</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="D49" s="30" t="s">
         <v>61</v>
@@ -2589,7 +2589,7 @@
         <v>22</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>26</v>
@@ -2603,10 +2603,10 @@
         <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -2628,13 +2628,13 @@
         <v>28</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -2642,13 +2642,13 @@
         <v>28</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -2670,13 +2670,13 @@
         <v>28</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -2684,13 +2684,13 @@
         <v>28</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -2712,13 +2712,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -2726,13 +2726,13 @@
         <v>28</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -2740,13 +2740,13 @@
         <v>28</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -2838,13 +2838,13 @@
         <v>39</v>
       </c>
       <c r="B68" s="30" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C68" s="30" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D68" s="33" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -2894,13 +2894,13 @@
         <v>39</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -2908,13 +2908,13 @@
         <v>39</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -2922,251 +2922,251 @@
         <v>39</v>
       </c>
       <c r="B74" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="C74" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="C74" s="30" t="s">
+      <c r="D74" s="30" t="s">
         <v>145</v>
-      </c>
-      <c r="D74" s="30" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" s="30" t="s">
         <v>224</v>
-      </c>
-      <c r="B75" s="30" t="s">
-        <v>225</v>
-      </c>
-      <c r="C75" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="D75" s="30" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A76" s="33" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D76" s="33" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="33" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" s="33" t="s">
         <v>234</v>
-      </c>
-      <c r="B78" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="C78" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="D78" s="33" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A79" s="33" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="30" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B80" s="35" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C81" s="30" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D81" s="33" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B82" s="30" t="s">
         <v>244</v>
       </c>
-      <c r="B82" s="30" t="s">
-        <v>247</v>
-      </c>
       <c r="C82" s="30" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D84" s="30" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="30" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -3191,12 +3191,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3212,18 +3212,18 @@
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="11" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>199</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3257,12 +3257,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -3283,7 +3283,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>78</v>
@@ -3301,16 +3301,16 @@
         <v>82</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>84</v>
@@ -3322,7 +3322,7 @@
         <v>86</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>87</v>
@@ -44286,12 +44286,12 @@
   <sheetData>
     <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.2">
@@ -44312,7 +44312,7 @@
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="X4" t="s">
         <v>16</v>
@@ -44327,27 +44327,27 @@
         <v>39</v>
       </c>
       <c r="BB4" s="37" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="BC4" s="37"/>
       <c r="BD4" s="37"/>
       <c r="BE4" s="37" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="BF4" s="37"/>
       <c r="BG4" s="37"/>
       <c r="BH4" s="37" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
       <c r="BK4" s="38" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
       <c r="BN4" s="38" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="BO4" s="38"/>
       <c r="BP4" s="38"/>
@@ -44362,34 +44362,34 @@
         <v>77</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>65</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="J5" s="36" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M5" s="36" t="s">
         <v>8</v>
@@ -44398,25 +44398,25 @@
         <v>13</v>
       </c>
       <c r="O5" s="36" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q5" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="R5" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="R5" s="36" t="s">
-        <v>111</v>
-      </c>
       <c r="S5" s="36" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="T5" s="46" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="V5" s="44" t="s">
         <v>9</v>
@@ -44425,7 +44425,7 @@
         <v>71</v>
       </c>
       <c r="X5" s="45" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Y5" s="44" t="s">
         <v>17</v>
@@ -44440,40 +44440,40 @@
         <v>21</v>
       </c>
       <c r="AC5" s="47" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AD5" s="47" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AE5" s="47" t="s">
         <v>67</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AG5" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="AH5" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="AI5" s="36" t="s">
+        <v>137</v>
+      </c>
+      <c r="AJ5" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK5" s="45" t="s">
         <v>134</v>
       </c>
-      <c r="AH5" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI5" s="36" t="s">
+      <c r="AL5" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="AM5" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="AJ5" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK5" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="AL5" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="AM5" s="45" t="s">
+      <c r="AN5" s="45" t="s">
         <v>139</v>
-      </c>
-      <c r="AN5" s="45" t="s">
-        <v>140</v>
       </c>
       <c r="AO5" s="36" t="s">
         <v>29</v>
@@ -44494,7 +44494,7 @@
         <v>35</v>
       </c>
       <c r="AU5" s="36" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="AV5" s="36" t="s">
         <v>36</v>
@@ -44506,64 +44506,64 @@
         <v>38</v>
       </c>
       <c r="AY5" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="AZ5" s="36" t="s">
         <v>218</v>
       </c>
-      <c r="AZ5" s="36" t="s">
-        <v>221</v>
-      </c>
       <c r="BA5" s="36" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="BB5" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="BC5" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="BC5" s="39" t="s">
+      <c r="BD5" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="BD5" s="39" t="s">
-        <v>231</v>
-      </c>
       <c r="BE5" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="BF5" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="BF5" s="39" t="s">
+      <c r="BG5" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="BG5" s="39" t="s">
-        <v>241</v>
-      </c>
       <c r="BH5" s="39" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="BI5" s="39" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="BJ5" s="39" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="BK5" s="39" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="BL5" s="39" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="BM5" s="39" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="BN5" s="39" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="BO5" s="39" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="BP5" s="39" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="BQ5" s="39" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="BR5" s="39" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.2">

--- a/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v19_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E4A7243-FBD9-6F40-BD1B-B67056456E25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F86E46F-48A4-3347-B197-BC2867EB940D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="19000" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="313">
   <si>
     <t>Field Name</t>
   </si>
@@ -263,20 +263,6 @@
     <t>Please fill out as many columns as possible. The GREEN SHADED columns are mandatory. See Data Dictionary sheet for a detailed description of each column.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Latitude of the actual sample location, in decimal degrees. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Note: in the southern hemisphere all latitudes must be negative. - If unknown please provide a central value based on the center of the waterbody. </t>
-    </r>
-  </si>
-  <si>
     <t>Name of the water body</t>
   </si>
   <si>
@@ -317,9 +303,6 @@
   </si>
   <si>
     <t>as in: 1; format: integer</t>
-  </si>
-  <si>
-    <t>Sex of the organism (e.g., male, female,  and unknown)</t>
   </si>
   <si>
     <t>Estimated age in years</t>
@@ -442,9 +425,6 @@
     <t>as in: 01; format: integer</t>
   </si>
   <si>
-    <t>Depth the sample was collected; please use meters</t>
-  </si>
-  <si>
     <t xml:space="preserve">as in: -27.23 ‰; format: integer; place to 2 decimals </t>
   </si>
   <si>
@@ -464,9 +444,6 @@
   </si>
   <si>
     <t xml:space="preserve">Method used for calorimetry </t>
-  </si>
-  <si>
-    <t>as in: parr microsemi oxygen bomb; format: character</t>
   </si>
   <si>
     <t>date</t>
@@ -601,9 +578,6 @@
     <t>as in: 750; format: integer</t>
   </si>
   <si>
-    <t xml:space="preserve">Weight of the sample </t>
-  </si>
-  <si>
     <t xml:space="preserve">as in: 5; format: integer </t>
   </si>
   <si>
@@ -635,45 +609,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sample origins (e.g., wild or lab) </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Longitude of the actual deployment location, in decimal degrees. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Note: in the western hemisphere all longitudes must be negative.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">-  If unknown please provide a central value based on the center of the waterbody.  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
   </si>
   <si>
     <t>publication_year</t>
@@ -754,9 +689,6 @@
     <t>as in: www.doi.org/10.1007/978-3-030-62259-6; format: character</t>
   </si>
   <si>
-    <t>as in: Lake Trout; format: character</t>
-  </si>
-  <si>
     <t>as in: Salvelinus namaycush; format: character</t>
   </si>
   <si>
@@ -784,12 +716,6 @@
     <t>as in: 1.412; format: numeric; places to 3 decimals</t>
   </si>
   <si>
-    <t xml:space="preserve">as in kJ/g wet weight; format: character </t>
-  </si>
-  <si>
-    <t xml:space="preserve">as in Wet mass; format: character </t>
-  </si>
-  <si>
     <t>as in: School of the Environment, University of Windsor, 2990 Riverside Dr W, Windsor, ON N9C 1A2, Canada / Glenora Fisheries Station, Ontario Ministry of Natural Resources, 41 Hatchery Lane, Picton, Ontario K0K 2T0, Canada; format: character</t>
   </si>
   <si>
@@ -797,9 +723,6 @@
   </si>
   <si>
     <t>as in: 5 (1-12); format: integer</t>
-  </si>
-  <si>
-    <t>as in: male - (i.e., male, female, unknown, &amp; mixed); format: character</t>
   </si>
   <si>
     <t xml:space="preserve">as in: Canadian Journal of Fisheries and Aquatic Sciences; format: character </t>
@@ -812,12 +735,6 @@
   </si>
   <si>
     <t>as in: 2009-02-26; format: POSIXct; places: yyyy-mm-dd</t>
-  </si>
-  <si>
-    <t>as in: Fork; format: character</t>
-  </si>
-  <si>
-    <t xml:space="preserve">as in 5237; format: numeric; places to 3 decimals </t>
   </si>
   <si>
     <t xml:space="preserve">as in: 43.84865; format: numeric; places: dd.ddddd to 5 decimals </t>
@@ -901,40 +818,16 @@
     <t>tbl_submission</t>
   </si>
   <si>
-    <t xml:space="preserve">Name of the person submitting the data </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Email address of submitting person </t>
-  </si>
-  <si>
     <t>as in: Benjamin L. Hlina; format: character</t>
-  </si>
-  <si>
-    <t>as in: juvenile - (i.e., fry, larva, juvenile, and adult); format: character</t>
   </si>
   <si>
     <t>Life stage (e.g., juvenile, adult)</t>
   </si>
   <si>
-    <t>For lab studies what was the treatment (e.g., control, diet #2, or T22degC)</t>
-  </si>
-  <si>
     <t>Length in millimetres (mm)</t>
   </si>
   <si>
-    <t>Weight of fish in grams (g)</t>
-  </si>
-  <si>
-    <t>Site the sample was collected assigned by the collector</t>
-  </si>
-  <si>
-    <t>Area the sample was collected assigned by the collector</t>
-  </si>
-  <si>
     <t>isotope_lipid_correction</t>
-  </si>
-  <si>
-    <t>Type of measurement for length (e.g., Fork, Total, Standard, or Carapace)</t>
   </si>
   <si>
     <t>Energy density measurement</t>
@@ -1129,31 +1022,7 @@
     <t>tbl_thiamine</t>
   </si>
   <si>
-    <t>Literature source id</t>
-  </si>
-  <si>
-    <t>Affiliation of submitting person</t>
-  </si>
-  <si>
-    <t>Affiliation of corresponding author</t>
-  </si>
-  <si>
-    <t>Genus and species of the organism</t>
-  </si>
-  <si>
-    <t>Type of sample procedure prior to analysis (dried, ground)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">as in: 1.35; format: numeric; places 2 decimals </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conversion factor for calorimetry </t>
-  </si>
-  <si>
     <t>The y-intercept for energy density equations</t>
-  </si>
-  <si>
-    <t>as in: control; format: character</t>
   </si>
   <si>
     <t>thiamine_type</t>
@@ -1201,9 +1070,6 @@
     <t>as in: Individual; format: character</t>
   </si>
   <si>
-    <t>Whether the sample is an Individual, Composite, Mean, SD, or Equation</t>
-  </si>
-  <si>
     <t>as in: bulk; format: character</t>
   </si>
   <si>
@@ -1218,6 +1084,150 @@
   <si>
     <t>This data dictionary is to guide you in filling out/interpreting the fields in tbl_submission, tbl_sources,  and tbl_samples data sheet. This sheet does not need to be submitted with your data. Green fields are required when submitting the data</t>
   </si>
+  <si>
+    <t>Constraints</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Journal Article, Book, Book Section, Report, Unpublished</t>
+  </si>
+  <si>
+    <t>If there is no known email address please use jane.doe@mail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If unpublished please put unpublished as the title </t>
+  </si>
+  <si>
+    <t>If there is no common name for a speices, genus, family ect. then use the scientific name (e.g., Diporia spp.)</t>
+  </si>
+  <si>
+    <t>male, female, unknown, or both</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fry, larva, nymph, pupa, juvenile, or adult </t>
+  </si>
+  <si>
+    <t xml:space="preserve">wild or lab </t>
+  </si>
+  <si>
+    <t>fork, total, standard, or carapace</t>
+  </si>
+  <si>
+    <t>individual, composite, mean, SD, or equation</t>
+  </si>
+  <si>
+    <t>belly flap, blood, carcass, cleithra, eye lens, egg, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), or whole body (stomach removed)</t>
+  </si>
+  <si>
+    <t>wet or dried</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the southern hemisphere all latitudes must be negative. - If unknown, please provide a central value based on the center of the waterbody. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the western hemisphere all longitudes must be negative. -  If unknown, please provide a central value based on the center of the waterbody.   </t>
+  </si>
+  <si>
+    <t>Parr oxygen bomb, Parr semi-micro oxygen bomb, Phillipson microbomb, Gentry-Weigert bomb, Unknown bomb, Proximate composition, Organic analysis, Wet digestion, or Unknown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wet or dry </t>
+  </si>
+  <si>
+    <t>Joules/g</t>
+  </si>
+  <si>
+    <t>bulk or lipid free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The name of person submitting the data </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The email address of person submitting the data  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">The affiliation of person submitting the data </t>
+  </si>
+  <si>
+    <t>Literature soruce id</t>
+  </si>
+  <si>
+    <t>Affilation of corresponding author</t>
+  </si>
+  <si>
+    <t>as in: Lake trout; format: character</t>
+  </si>
+  <si>
+    <t>Genus and speices of the organism</t>
+  </si>
+  <si>
+    <t>as in: male; format: character</t>
+  </si>
+  <si>
+    <t>Sex of the organism (e.g., male or female)</t>
+  </si>
+  <si>
+    <t>as in: juvenile; format: character</t>
+  </si>
+  <si>
+    <t>as in: control: format: character</t>
+  </si>
+  <si>
+    <t>For lab studies, what was the treatment (e.g., control, diet #2, or T22degC)</t>
+  </si>
+  <si>
+    <t>as in: fork; format: character</t>
+  </si>
+  <si>
+    <t>Type of measurement for length (e.g., fork, total, standard, or carapace)</t>
+  </si>
+  <si>
+    <t>Weight of organism in grams (g)</t>
+  </si>
+  <si>
+    <t>Whether the sample is an Individual organism, Composite of multiple individuals, Mean, SD, or Equation</t>
+  </si>
+  <si>
+    <t>Type of sample procudure prior to anlysis (dried, ground)</t>
+  </si>
+  <si>
+    <t>Area where sample was collected assigned by the collector</t>
+  </si>
+  <si>
+    <t>Site where sample was collected assigned by the collector</t>
+  </si>
+  <si>
+    <t>Depth where sample was collected; please use meters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude of the actual sample location, in decimal degrees. </t>
+  </si>
+  <si>
+    <t>Longitude of the actual sample location, in decimal degrees.</t>
+  </si>
+  <si>
+    <t>as in: parr semi-micro oxygen bomb; format: character</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as in: 1.35; format: numeric; places 2 decmials </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Converstion factor for calorimetry </t>
+  </si>
+  <si>
+    <t>Weight of the sample (in grams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">as in: 5237; format: numeric; places to 3 decimals </t>
+  </si>
+  <si>
+    <t xml:space="preserve">as in: kJ/g wet weight; format: character </t>
+  </si>
+  <si>
+    <t xml:space="preserve">as in: wet weight in g; format: character </t>
+  </si>
 </sst>
 </file>
 
@@ -1226,7 +1236,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1268,12 +1278,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1444,10 +1448,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1471,105 +1475,106 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1911,33 +1916,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDB0B4B-8041-E244-B061-95D35DE0CD3B}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D91"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" style="1" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.5" style="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="1"/>
+    <col min="5" max="5" width="32" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="48" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
       <c r="D1" s="48"/>
     </row>
-    <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="48" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
@@ -1950,582 +1957,692 @@
       <c r="D4" s="18" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" s="51" t="s">
+        <v>265</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>284</v>
+      </c>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="56" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+    </row>
+    <row r="7" spans="1:6" ht="56" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+    </row>
+    <row r="9" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="B9" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="F9" s="30"/>
+    </row>
+    <row r="10" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+    </row>
+    <row r="11" spans="1:6" ht="56" x14ac:dyDescent="0.2">
+      <c r="A11" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+    </row>
+    <row r="12" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+      <c r="A12" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="30"/>
+      <c r="F12" s="33" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A13" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B13" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C13" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="30"/>
+      <c r="F13" s="33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="24" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B10" s="27" t="s">
+      <c r="D14" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B15" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="56" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B11" s="24" t="s">
+      <c r="C15" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B18" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B12" s="27" t="s">
+      <c r="C18" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B19" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="C19" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+    </row>
+    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A20" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B20" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B15" s="24" t="s">
+      <c r="C20" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B22" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="D15" s="24" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="24" t="s">
+      <c r="C22" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B17" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A20" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="D22" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="25" t="s">
-        <v>291</v>
-      </c>
-      <c r="B22" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="24" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C24" s="30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="30" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+    </row>
+    <row r="29" spans="1:6" ht="56" x14ac:dyDescent="0.2">
       <c r="A29" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B29" s="32" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>153</v>
+        <v>289</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E29" s="30"/>
+      <c r="F29" s="33" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>290</v>
+      </c>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>168</v>
+        <v>291</v>
       </c>
       <c r="D33" s="30" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>292</v>
+      </c>
+      <c r="E33" s="30" t="s">
+        <v>271</v>
+      </c>
+      <c r="F33" s="30"/>
+    </row>
+    <row r="34" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+        <v>191</v>
+      </c>
+      <c r="E34" s="33" t="s">
+        <v>272</v>
+      </c>
+      <c r="F34" s="30"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>13</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+      <c r="E35" s="30" t="s">
+        <v>273</v>
+      </c>
+      <c r="F35" s="30"/>
+    </row>
+    <row r="36" spans="1:6" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+        <v>295</v>
+      </c>
+      <c r="E36" s="30"/>
+      <c r="F36" s="30"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="C37" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C38" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="D37" s="30" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B38" s="30" t="s">
+      <c r="D38" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
+    </row>
+    <row r="39" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A39" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B39" s="30" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="E39" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="F39" s="30"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B40" s="30" t="s">
+        <v>183</v>
+      </c>
+      <c r="C40" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="C38" s="30" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A39" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>173</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="B40" s="30" t="s">
-        <v>195</v>
-      </c>
-      <c r="C40" s="30" t="s">
-        <v>113</v>
-      </c>
       <c r="D40" s="30" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="28" x14ac:dyDescent="0.2">
+        <v>298</v>
+      </c>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+    </row>
+    <row r="41" spans="1:6" ht="42" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+        <v>299</v>
+      </c>
+      <c r="E41" s="33" t="s">
+        <v>275</v>
+      </c>
+      <c r="F41" s="30"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="C42" s="30" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D42" s="30" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+      <c r="E42" s="30"/>
+      <c r="F42" s="30"/>
+    </row>
+    <row r="43" spans="1:6" ht="84" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B43" s="32" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" s="33" t="s">
+        <v>276</v>
+      </c>
+      <c r="F43" s="30"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="E44" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="F44" s="30"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="30" t="s">
         <v>16</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C45" s="30" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D45" s="30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="E45" s="30"/>
+      <c r="F45" s="30"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="30" t="s">
         <v>16</v>
       </c>
@@ -2533,13 +2650,15 @@
         <v>17</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="30" t="s">
         <v>16</v>
       </c>
@@ -2547,13 +2666,15 @@
         <v>19</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="30" t="s">
         <v>16</v>
       </c>
@@ -2561,13 +2682,15 @@
         <v>20</v>
       </c>
       <c r="C48" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+      <c r="E48" s="30"/>
+      <c r="F48" s="30"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="30" t="s">
         <v>16</v>
       </c>
@@ -2575,13 +2698,15 @@
         <v>21</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D49" s="30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="56" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+    </row>
+    <row r="50" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A50" s="30" t="s">
         <v>16</v>
       </c>
@@ -2589,13 +2714,17 @@
         <v>22</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="56" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+      <c r="E50" s="30"/>
+      <c r="F50" s="33" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A51" s="30" t="s">
         <v>16</v>
       </c>
@@ -2603,571 +2732,663 @@
         <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+      <c r="E51" s="30"/>
+      <c r="F51" s="33" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="70" x14ac:dyDescent="0.2">
       <c r="A52" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E52" s="33" t="s">
+        <v>280</v>
+      </c>
+      <c r="F52" s="30"/>
+    </row>
+    <row r="53" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A53" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E53" s="30"/>
+      <c r="F53" s="30"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="C54" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="E54" s="30"/>
+      <c r="F54" s="30"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="C55" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="D55" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="F55" s="30"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>131</v>
+      </c>
+      <c r="C56" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D56" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="E56" s="30"/>
+      <c r="F56" s="30"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B57" s="35" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="D57" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>282</v>
+      </c>
+      <c r="F57" s="30"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>310</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+    </row>
+    <row r="60" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A60" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B60" s="35" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="30" t="s">
+        <v>311</v>
+      </c>
+      <c r="D60" s="33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="30"/>
+      <c r="F60" s="30"/>
+    </row>
+    <row r="61" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A61" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>136</v>
+      </c>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="B52" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A53" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>133</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="C55" s="30" t="s">
-        <v>161</v>
-      </c>
-      <c r="D55" s="30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B56" s="30" t="s">
+      <c r="C62" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D63" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="30" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D65" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E65" s="30"/>
+      <c r="F65" s="30"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C66" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="30"/>
+      <c r="F66" s="30"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C67" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+    </row>
+    <row r="68" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A68" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>260</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E68" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="F68" s="30"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C69" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="30"/>
+      <c r="F69" s="30"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C70" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="D70" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C71" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D71" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="C72" s="30" t="s">
+        <v>199</v>
+      </c>
+      <c r="D72" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" s="30"/>
+      <c r="F72" s="30"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A73" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="30" t="s">
+        <v>198</v>
+      </c>
+      <c r="C73" s="30" t="s">
+        <v>200</v>
+      </c>
+      <c r="D73" s="30" t="s">
+        <v>197</v>
+      </c>
+      <c r="E73" s="30"/>
+      <c r="F73" s="30"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A74" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="C56" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="D56" s="30" t="s">
+      <c r="C74" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="D74" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="E74" s="30"/>
+      <c r="F74" s="30"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A75" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B75" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="30" t="s">
+        <v>203</v>
+      </c>
+      <c r="D75" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="E75" s="30"/>
+      <c r="F75" s="30"/>
+    </row>
+    <row r="76" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A76" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B76" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D76" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="B77" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="E77" s="30"/>
+      <c r="F77" s="30"/>
+    </row>
+    <row r="78" spans="1:6" ht="28" x14ac:dyDescent="0.2">
+      <c r="A78" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C78" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" s="33" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B57" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="D57" s="30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B58" s="30" t="s">
-        <v>134</v>
-      </c>
-      <c r="C58" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" s="30" t="s">
-        <v>174</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B60" s="35" t="s">
-        <v>138</v>
-      </c>
-      <c r="C60" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B61" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="C61" s="30" t="s">
-        <v>164</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>29</v>
-      </c>
-      <c r="C62" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B63" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="D63" s="30" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B64" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C64" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D64" s="30" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B65" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C65" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B66" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="C66" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D66" s="30" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B67" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" s="30" t="s">
-        <v>52</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A68" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="C68" s="30" t="s">
-        <v>289</v>
-      </c>
-      <c r="D68" s="33" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C69" s="30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D69" s="30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="D70" s="30" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B71" s="30" t="s">
-        <v>38</v>
-      </c>
-      <c r="C71" s="30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D71" s="30" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B72" s="30" t="s">
+      <c r="E78" s="30"/>
+      <c r="F78" s="30"/>
+    </row>
+    <row r="79" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+      <c r="A79" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="B79" s="34" t="s">
         <v>215</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C79" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="E79" s="30"/>
+      <c r="F79" s="30"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="B80" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="30" t="s">
         <v>219</v>
       </c>
-      <c r="D72" s="30" t="s">
+      <c r="D80" s="30" t="s">
+        <v>220</v>
+      </c>
+      <c r="E80" s="30"/>
+      <c r="F80" s="30"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="E81" s="30"/>
+      <c r="F81" s="30"/>
+    </row>
+    <row r="82" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+      <c r="A82" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B82" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" s="30" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B73" s="30" t="s">
-        <v>218</v>
-      </c>
-      <c r="C73" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="D73" s="30" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="30" t="s">
-        <v>39</v>
-      </c>
-      <c r="B74" s="30" t="s">
-        <v>143</v>
-      </c>
-      <c r="C74" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="D74" s="30" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="30" t="s">
+      <c r="D82" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="E82" s="30"/>
+      <c r="F82" s="30"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="30" t="s">
         <v>221</v>
       </c>
-      <c r="B75" s="30" t="s">
-        <v>222</v>
-      </c>
-      <c r="C75" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="D75" s="30" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A76" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="B76" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="C76" s="33" t="s">
+      <c r="B83" s="30" t="s">
         <v>226</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="C83" s="30" t="s">
+        <v>252</v>
+      </c>
+      <c r="D83" s="33" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="B77" s="33" t="s">
+      <c r="E83" s="30"/>
+      <c r="F83" s="30"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B84" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="C77" s="33" t="s">
+      <c r="C84" s="30" t="s">
+        <v>248</v>
+      </c>
+      <c r="D84" s="30" t="s">
         <v>229</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="E84" s="30"/>
+      <c r="F84" s="30"/>
+    </row>
+    <row r="85" spans="1:6" ht="42" x14ac:dyDescent="0.2">
+      <c r="A85" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B85" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>247</v>
+      </c>
+      <c r="E85" s="30"/>
+      <c r="F85" s="30"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="30" t="s">
+        <v>243</v>
+      </c>
+      <c r="B86" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="C86" s="30" t="s">
+        <v>250</v>
+      </c>
+      <c r="D86" s="30" t="s">
+        <v>251</v>
+      </c>
+      <c r="E86" s="30"/>
+      <c r="F86" s="30"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B87" s="30" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" ht="28" x14ac:dyDescent="0.2">
-      <c r="A78" s="33" t="s">
+      <c r="C87" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="D87" s="30" t="s">
         <v>231</v>
       </c>
-      <c r="B78" s="34" t="s">
+      <c r="E87" s="30"/>
+      <c r="F87" s="30"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B88" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="C78" s="33" t="s">
+      <c r="C88" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="D88" s="30" t="s">
         <v>233</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="E88" s="30"/>
+      <c r="F88" s="30"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B89" s="30" t="s">
+        <v>242</v>
+      </c>
+      <c r="C89" s="30" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" ht="42" x14ac:dyDescent="0.2">
-      <c r="A79" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="B79" s="34" t="s">
+      <c r="D89" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="C79" s="33" t="s">
+      <c r="E89" s="30"/>
+      <c r="F89" s="30"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B90" s="30" t="s">
         <v>236</v>
       </c>
-      <c r="D79" s="33" t="s">
+      <c r="C90" s="30" t="s">
+        <v>255</v>
+      </c>
+      <c r="D90" s="30" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="B80" s="35" t="s">
+      <c r="E90" s="30"/>
+      <c r="F90" s="30"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="30" t="s">
+        <v>241</v>
+      </c>
+      <c r="B91" s="30" t="s">
         <v>238</v>
       </c>
-      <c r="C80" s="30" t="s">
+      <c r="C91" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="D80" s="30" t="s">
+      <c r="D91" s="30" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B81" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>284</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" ht="42" x14ac:dyDescent="0.2">
-      <c r="A82" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B82" s="30" t="s">
-        <v>244</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>236</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="30" t="s">
-        <v>241</v>
-      </c>
-      <c r="B83" s="30" t="s">
-        <v>246</v>
-      </c>
-      <c r="C83" s="30" t="s">
-        <v>280</v>
-      </c>
-      <c r="D83" s="33" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="B84" s="30" t="s">
-        <v>248</v>
-      </c>
-      <c r="C84" s="30" t="s">
-        <v>276</v>
-      </c>
-      <c r="D84" s="30" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.2">
-      <c r="A85" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="B85" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>277</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="30" t="s">
-        <v>263</v>
-      </c>
-      <c r="B86" s="40" t="s">
-        <v>274</v>
-      </c>
-      <c r="C86" s="30" t="s">
-        <v>278</v>
-      </c>
-      <c r="D86" s="30" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B87" s="30" t="s">
-        <v>250</v>
-      </c>
-      <c r="C87" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="D87" s="30" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B88" s="30" t="s">
-        <v>252</v>
-      </c>
-      <c r="C88" s="30" t="s">
-        <v>281</v>
-      </c>
-      <c r="D88" s="30" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B89" s="30" t="s">
-        <v>262</v>
-      </c>
-      <c r="C89" s="30" t="s">
-        <v>254</v>
-      </c>
-      <c r="D89" s="30" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B90" s="30" t="s">
-        <v>256</v>
-      </c>
-      <c r="C90" s="30" t="s">
-        <v>283</v>
-      </c>
-      <c r="D90" s="30" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="30" t="s">
-        <v>261</v>
-      </c>
-      <c r="B91" s="30" t="s">
-        <v>258</v>
-      </c>
-      <c r="C91" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="D91" s="30" t="s">
-        <v>260</v>
-      </c>
+      <c r="E91" s="30"/>
+      <c r="F91" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3191,12 +3412,12 @@
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -3212,18 +3433,18 @@
       <c r="B3" s="49"/>
       <c r="C3" s="49"/>
       <c r="D3" s="11" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3257,12 +3478,12 @@
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
@@ -3283,49 +3504,49 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="G4" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="I4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="L4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="N4" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -44286,12 +44507,12 @@
   <sheetData>
     <row r="1" spans="1:70" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
       <c r="D1" s="5" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:70" x14ac:dyDescent="0.2">
@@ -44312,42 +44533,42 @@
     </row>
     <row r="4" spans="1:70" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="X4" t="s">
         <v>16</v>
       </c>
       <c r="AE4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="BB4" s="37" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="BC4" s="37"/>
       <c r="BD4" s="37"/>
       <c r="BE4" s="37" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="BF4" s="37"/>
       <c r="BG4" s="37"/>
       <c r="BH4" s="37" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
       <c r="BK4" s="38" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
       <c r="BN4" s="38" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="BO4" s="38"/>
       <c r="BP4" s="38"/>
@@ -44359,37 +44580,37 @@
         <v>14</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="J5" s="36" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="M5" s="36" t="s">
         <v>8</v>
@@ -44398,34 +44619,34 @@
         <v>13</v>
       </c>
       <c r="O5" s="36" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="S5" s="36" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="T5" s="46" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="V5" s="44" t="s">
         <v>9</v>
       </c>
       <c r="W5" s="46" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="X5" s="45" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="Y5" s="44" t="s">
         <v>17</v>
@@ -44440,130 +44661,130 @@
         <v>21</v>
       </c>
       <c r="AC5" s="47" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="AD5" s="47" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="AE5" s="47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="AG5" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="AH5" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="AI5" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ5" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="AK5" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="AL5" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM5" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="AN5" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="AH5" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="AI5" s="36" t="s">
+      <c r="AO5" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="AP5" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ5" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="AR5" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS5" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT5" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="AU5" s="36" t="s">
+        <v>193</v>
+      </c>
+      <c r="AV5" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="AW5" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="AX5" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="AY5" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="AZ5" s="36" t="s">
+        <v>198</v>
+      </c>
+      <c r="BA5" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="AJ5" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="AK5" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="AL5" s="45" t="s">
-        <v>135</v>
-      </c>
-      <c r="AM5" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="AN5" s="45" t="s">
-        <v>139</v>
-      </c>
-      <c r="AO5" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="AP5" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="AQ5" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="AR5" s="36" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS5" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="AT5" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="AU5" s="36" t="s">
+      <c r="BB5" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="BC5" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="BD5" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="BE5" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="AV5" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="AW5" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="AX5" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="AY5" s="36" t="s">
+      <c r="BF5" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="AZ5" s="36" t="s">
+      <c r="BG5" s="39" t="s">
         <v>218</v>
       </c>
-      <c r="BA5" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="BB5" s="39" t="s">
+      <c r="BH5" s="39" t="s">
         <v>222</v>
       </c>
-      <c r="BC5" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="BD5" s="39" t="s">
+      <c r="BI5" s="39" t="s">
+        <v>224</v>
+      </c>
+      <c r="BJ5" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="BK5" s="39" t="s">
         <v>228</v>
       </c>
-      <c r="BE5" s="39" t="s">
+      <c r="BL5" s="39" t="s">
+        <v>245</v>
+      </c>
+      <c r="BM5" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN5" s="39" t="s">
+        <v>230</v>
+      </c>
+      <c r="BO5" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="BF5" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="BG5" s="39" t="s">
+      <c r="BP5" s="39" t="s">
+        <v>242</v>
+      </c>
+      <c r="BQ5" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="BR5" s="39" t="s">
         <v>238</v>
-      </c>
-      <c r="BH5" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="BI5" s="39" t="s">
-        <v>244</v>
-      </c>
-      <c r="BJ5" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="BK5" s="39" t="s">
-        <v>248</v>
-      </c>
-      <c r="BL5" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="BM5" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="BN5" s="39" t="s">
-        <v>250</v>
-      </c>
-      <c r="BO5" s="39" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP5" s="39" t="s">
-        <v>262</v>
-      </c>
-      <c r="BQ5" s="39" t="s">
-        <v>256</v>
-      </c>
-      <c r="BR5" s="39" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:70" x14ac:dyDescent="0.2">
